--- a/artfynd/A 53786-2025 artfynd.xlsx
+++ b/artfynd/A 53786-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,6 +781,1217 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129930882</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98790</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 53786, Lidhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>561722</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6401786</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129930852</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92252</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 53786, Lidhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>561682</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6401756</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129930947</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98790</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 53786, Lidhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>561757</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6401792</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129931032</v>
+      </c>
+      <c r="B6" t="n">
+        <v>105856</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 53786, Lidhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>561896</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6401700</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129930843</v>
+      </c>
+      <c r="B7" t="n">
+        <v>105856</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 53786, Lidhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>561629</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6401757</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129930889</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98790</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 53786, Lidhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>561735</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6401780</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129934871</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 53786, Lidhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>561819</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6401743</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129930871</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98790</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 53786, Lidhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>561719</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6401782</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129930865</v>
+      </c>
+      <c r="B11" t="n">
+        <v>105856</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 53786, Lidhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>561719</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6401782</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129934882</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 53786, Lidhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>561896</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6401701</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129931017</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92031</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 53786, Lidhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>561760</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6401769</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53786-2025 artfynd.xlsx
+++ b/artfynd/A 53786-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129919814</v>
       </c>
       <c r="B2" t="n">
-        <v>57730</v>
+        <v>57731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129930882</v>
       </c>
       <c r="B3" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129930852</v>
       </c>
       <c r="B4" t="n">
-        <v>92252</v>
+        <v>92255</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>129930947</v>
       </c>
       <c r="B5" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129931032</v>
+        <v>129930843</v>
       </c>
       <c r="B6" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561896</v>
+        <v>561629</v>
       </c>
       <c r="R6" t="n">
-        <v>6401700</v>
+        <v>6401757</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129930843</v>
+        <v>129931032</v>
       </c>
       <c r="B7" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561629</v>
+        <v>561896</v>
       </c>
       <c r="R7" t="n">
-        <v>6401757</v>
+        <v>6401700</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
         <v>129930889</v>
       </c>
       <c r="B8" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>129934871</v>
       </c>
       <c r="B9" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>129930871</v>
       </c>
       <c r="B10" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,46 +1667,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129930865</v>
+        <v>129934882</v>
       </c>
       <c r="B11" t="n">
-        <v>105856</v>
+        <v>57895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1714,13 +1714,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561719</v>
+        <v>561896</v>
       </c>
       <c r="R11" t="n">
-        <v>6401782</v>
+        <v>6401701</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,7 +1758,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,46 +1776,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129934882</v>
+        <v>129930865</v>
       </c>
       <c r="B12" t="n">
-        <v>57896</v>
+        <v>105860</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1824,13 +1823,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>561896</v>
+        <v>561719</v>
       </c>
       <c r="R12" t="n">
-        <v>6401701</v>
+        <v>6401782</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1868,6 +1867,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1889,7 +1889,7 @@
         <v>129931017</v>
       </c>
       <c r="B13" t="n">
-        <v>92031</v>
+        <v>92034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 53786-2025 artfynd.xlsx
+++ b/artfynd/A 53786-2025 artfynd.xlsx
@@ -1118,7 +1118,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129930843</v>
+        <v>129931032</v>
       </c>
       <c r="B6" t="n">
         <v>105860</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561629</v>
+        <v>561896</v>
       </c>
       <c r="R6" t="n">
-        <v>6401757</v>
+        <v>6401700</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129931032</v>
+        <v>129930843</v>
       </c>
       <c r="B7" t="n">
         <v>105860</v>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561896</v>
+        <v>561629</v>
       </c>
       <c r="R7" t="n">
-        <v>6401700</v>
+        <v>6401757</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,46 +1338,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129930889</v>
+        <v>129934871</v>
       </c>
       <c r="B8" t="n">
-        <v>98794</v>
+        <v>57895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561735</v>
+        <v>561819</v>
       </c>
       <c r="R8" t="n">
-        <v>6401780</v>
+        <v>6401743</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,7 +1429,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1448,46 +1447,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129934871</v>
+        <v>129930889</v>
       </c>
       <c r="B9" t="n">
-        <v>57895</v>
+        <v>98794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1495,13 +1494,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561819</v>
+        <v>561735</v>
       </c>
       <c r="R9" t="n">
-        <v>6401743</v>
+        <v>6401780</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1539,6 +1538,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53786-2025 artfynd.xlsx
+++ b/artfynd/A 53786-2025 artfynd.xlsx
@@ -1338,46 +1338,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129934871</v>
+        <v>129930889</v>
       </c>
       <c r="B8" t="n">
-        <v>57895</v>
+        <v>98794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561819</v>
+        <v>561735</v>
       </c>
       <c r="R8" t="n">
-        <v>6401743</v>
+        <v>6401780</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,6 +1429,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1447,46 +1448,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129930889</v>
+        <v>129934871</v>
       </c>
       <c r="B9" t="n">
-        <v>98794</v>
+        <v>57895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1494,13 +1495,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561735</v>
+        <v>561819</v>
       </c>
       <c r="R9" t="n">
-        <v>6401780</v>
+        <v>6401743</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,7 +1539,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53786-2025 artfynd.xlsx
+++ b/artfynd/A 53786-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129919814</v>
       </c>
       <c r="B2" t="n">
-        <v>57731</v>
+        <v>57734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129930882</v>
       </c>
       <c r="B3" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129930852</v>
       </c>
       <c r="B4" t="n">
-        <v>92255</v>
+        <v>92258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>129930947</v>
       </c>
       <c r="B5" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>129931032</v>
       </c>
       <c r="B6" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>129930843</v>
       </c>
       <c r="B7" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>129930889</v>
       </c>
       <c r="B8" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>129934871</v>
       </c>
       <c r="B9" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>129930871</v>
       </c>
       <c r="B10" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,46 +1667,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129934882</v>
+        <v>129930865</v>
       </c>
       <c r="B11" t="n">
-        <v>57895</v>
+        <v>105863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1714,13 +1714,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561896</v>
+        <v>561719</v>
       </c>
       <c r="R11" t="n">
-        <v>6401701</v>
+        <v>6401782</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,6 +1758,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1776,46 +1777,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129930865</v>
+        <v>129934882</v>
       </c>
       <c r="B12" t="n">
-        <v>105860</v>
+        <v>57898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1823,13 +1824,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>561719</v>
+        <v>561896</v>
       </c>
       <c r="R12" t="n">
-        <v>6401782</v>
+        <v>6401701</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1867,7 +1868,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1889,7 +1889,7 @@
         <v>129931017</v>
       </c>
       <c r="B13" t="n">
-        <v>92034</v>
+        <v>92037</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 53786-2025 artfynd.xlsx
+++ b/artfynd/A 53786-2025 artfynd.xlsx
@@ -1667,46 +1667,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129930865</v>
+        <v>129934882</v>
       </c>
       <c r="B11" t="n">
-        <v>105863</v>
+        <v>57898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1714,13 +1714,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561719</v>
+        <v>561896</v>
       </c>
       <c r="R11" t="n">
-        <v>6401782</v>
+        <v>6401701</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,7 +1758,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,46 +1776,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129934882</v>
+        <v>129930865</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>105863</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1824,13 +1823,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>561896</v>
+        <v>561719</v>
       </c>
       <c r="R12" t="n">
-        <v>6401701</v>
+        <v>6401782</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1868,6 +1867,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53786-2025 artfynd.xlsx
+++ b/artfynd/A 53786-2025 artfynd.xlsx
@@ -1338,46 +1338,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129930889</v>
+        <v>129934871</v>
       </c>
       <c r="B8" t="n">
-        <v>98797</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561735</v>
+        <v>561819</v>
       </c>
       <c r="R8" t="n">
-        <v>6401780</v>
+        <v>6401743</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,7 +1429,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1448,46 +1447,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129934871</v>
+        <v>129930889</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>98797</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1495,13 +1494,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561819</v>
+        <v>561735</v>
       </c>
       <c r="R9" t="n">
-        <v>6401743</v>
+        <v>6401780</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1539,6 +1538,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53786-2025 artfynd.xlsx
+++ b/artfynd/A 53786-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>129930882</v>
       </c>
       <c r="B3" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129930852</v>
       </c>
       <c r="B4" t="n">
-        <v>92258</v>
+        <v>92259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>129930947</v>
       </c>
       <c r="B5" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>129931032</v>
       </c>
       <c r="B6" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>129930843</v>
       </c>
       <c r="B7" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>129930889</v>
       </c>
       <c r="B9" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>129930871</v>
       </c>
       <c r="B10" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>129930865</v>
       </c>
       <c r="B12" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>129931017</v>
       </c>
       <c r="B13" t="n">
-        <v>92037</v>
+        <v>92038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 53786-2025 artfynd.xlsx
+++ b/artfynd/A 53786-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>129930882</v>
       </c>
       <c r="B3" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129930852</v>
       </c>
       <c r="B4" t="n">
-        <v>92259</v>
+        <v>92276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>129930947</v>
       </c>
       <c r="B5" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>129931032</v>
       </c>
       <c r="B6" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>129930843</v>
       </c>
       <c r="B7" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,46 +1338,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129934871</v>
+        <v>129930889</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>98815</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561819</v>
+        <v>561735</v>
       </c>
       <c r="R8" t="n">
-        <v>6401743</v>
+        <v>6401780</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,6 +1429,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1447,46 +1448,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129930889</v>
+        <v>129934871</v>
       </c>
       <c r="B9" t="n">
-        <v>98798</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1494,13 +1495,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561735</v>
+        <v>561819</v>
       </c>
       <c r="R9" t="n">
-        <v>6401780</v>
+        <v>6401743</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,7 +1539,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>129930871</v>
       </c>
       <c r="B10" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>129934882</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>129930865</v>
       </c>
       <c r="B12" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>129931017</v>
       </c>
       <c r="B13" t="n">
-        <v>92038</v>
+        <v>92055</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 53786-2025 artfynd.xlsx
+++ b/artfynd/A 53786-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>129930882</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -902,7 +902,7 @@
         <v>129930852</v>
       </c>
       <c r="B4" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>129930947</v>
       </c>
       <c r="B5" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1121,7 +1121,7 @@
         <v>129931032</v>
       </c>
       <c r="B6" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>129930843</v>
       </c>
       <c r="B7" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>129930889</v>
       </c>
       <c r="B9" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1560,7 +1560,7 @@
         <v>129930871</v>
       </c>
       <c r="B10" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1779,7 +1779,7 @@
         <v>129930865</v>
       </c>
       <c r="B12" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1889,7 +1889,7 @@
         <v>129931017</v>
       </c>
       <c r="B13" t="n">
-        <v>92071</v>
+        <v>92073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 53786-2025 artfynd.xlsx
+++ b/artfynd/A 53786-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129919814</v>
       </c>
       <c r="B2" t="n">
-        <v>57735</v>
+        <v>57820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129930882</v>
       </c>
       <c r="B3" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129930852</v>
       </c>
       <c r="B4" t="n">
-        <v>92294</v>
+        <v>92381</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>129930947</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>129931032</v>
       </c>
       <c r="B6" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>129930843</v>
       </c>
       <c r="B7" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>129934871</v>
       </c>
       <c r="B8" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>129930889</v>
       </c>
       <c r="B9" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>129930871</v>
       </c>
       <c r="B10" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>129934882</v>
       </c>
       <c r="B11" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>129930865</v>
       </c>
       <c r="B12" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>129931017</v>
       </c>
       <c r="B13" t="n">
-        <v>92073</v>
+        <v>92160</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 53786-2025 artfynd.xlsx
+++ b/artfynd/A 53786-2025 artfynd.xlsx
@@ -1667,46 +1667,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129934882</v>
+        <v>129930865</v>
       </c>
       <c r="B11" t="n">
-        <v>57985</v>
+        <v>105987</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1714,13 +1714,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561896</v>
+        <v>561719</v>
       </c>
       <c r="R11" t="n">
-        <v>6401701</v>
+        <v>6401782</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,6 +1758,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1776,46 +1777,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129930865</v>
+        <v>129934882</v>
       </c>
       <c r="B12" t="n">
-        <v>105987</v>
+        <v>57985</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1823,13 +1824,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>561719</v>
+        <v>561896</v>
       </c>
       <c r="R12" t="n">
-        <v>6401782</v>
+        <v>6401701</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1867,7 +1868,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53786-2025 artfynd.xlsx
+++ b/artfynd/A 53786-2025 artfynd.xlsx
@@ -1338,46 +1338,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129934871</v>
+        <v>129930889</v>
       </c>
       <c r="B8" t="n">
-        <v>57985</v>
+        <v>98920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561819</v>
+        <v>561735</v>
       </c>
       <c r="R8" t="n">
-        <v>6401743</v>
+        <v>6401780</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,6 +1429,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1447,46 +1448,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129930889</v>
+        <v>129934871</v>
       </c>
       <c r="B9" t="n">
-        <v>98920</v>
+        <v>57985</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1494,13 +1495,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561735</v>
+        <v>561819</v>
       </c>
       <c r="R9" t="n">
-        <v>6401780</v>
+        <v>6401743</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,7 +1539,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1667,46 +1667,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129930865</v>
+        <v>129934882</v>
       </c>
       <c r="B11" t="n">
-        <v>105987</v>
+        <v>57985</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1714,13 +1714,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561719</v>
+        <v>561896</v>
       </c>
       <c r="R11" t="n">
-        <v>6401782</v>
+        <v>6401701</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,7 +1758,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,46 +1776,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129934882</v>
+        <v>129930865</v>
       </c>
       <c r="B12" t="n">
-        <v>57985</v>
+        <v>105987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1824,13 +1823,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>561896</v>
+        <v>561719</v>
       </c>
       <c r="R12" t="n">
-        <v>6401701</v>
+        <v>6401782</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1868,6 +1867,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53786-2025 artfynd.xlsx
+++ b/artfynd/A 53786-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129919814</v>
       </c>
       <c r="B2" t="n">
-        <v>57820</v>
+        <v>57735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129930882</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129930852</v>
       </c>
       <c r="B4" t="n">
-        <v>92381</v>
+        <v>92294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>129930947</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>129931032</v>
       </c>
       <c r="B6" t="n">
-        <v>105987</v>
+        <v>105900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>129930843</v>
       </c>
       <c r="B7" t="n">
-        <v>105987</v>
+        <v>105900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,46 +1338,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129930889</v>
+        <v>129934871</v>
       </c>
       <c r="B8" t="n">
-        <v>98920</v>
+        <v>57900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561735</v>
+        <v>561819</v>
       </c>
       <c r="R8" t="n">
-        <v>6401780</v>
+        <v>6401743</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,7 +1429,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1448,46 +1447,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129934871</v>
+        <v>129930889</v>
       </c>
       <c r="B9" t="n">
-        <v>57985</v>
+        <v>98833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1495,13 +1494,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561819</v>
+        <v>561735</v>
       </c>
       <c r="R9" t="n">
-        <v>6401743</v>
+        <v>6401780</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1539,6 +1538,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>129930871</v>
       </c>
       <c r="B10" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>129934882</v>
       </c>
       <c r="B11" t="n">
-        <v>57985</v>
+        <v>57900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>129930865</v>
       </c>
       <c r="B12" t="n">
-        <v>105987</v>
+        <v>105900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>129931017</v>
       </c>
       <c r="B13" t="n">
-        <v>92160</v>
+        <v>92073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
